--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0001.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0001.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="58" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="59" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6 â€³</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+4FE1 CJK UNIFIED IDEOGRAPH-4FE1 | isolated marker/symbol line :: 信</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” = _ =</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]IMAGE EVALUATION</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]IMAGE EVALUATION</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 2</t>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,22 +670,26 @@
           <t>L16: suspicious token(s): IIl6 (letter/digit mix) :: ||.25 ||I.4 IIl6</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+6536 CJK UNIFIED IDEOGRAPH-6536 | isolated marker/symbol line :: 收</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Hâ€¢ MAS</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: H• MAS</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L2: isolated marker/symbol line :: ä¿¡</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+4FE1 CJK UNIFIED IDEOGRAPH-4FE1 | isolated marker/symbol line :: 信</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: 6"</t>
+          <t>L12: symbol-only separator/garbage line :: — = _ =</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -723,12 +731,12 @@
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L3: isolated marker/symbol line :: æ”¶</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+6536 CJK UNIFIED IDEOGRAPH-6536 | isolated marker/symbol line :: 收</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L30: symbol-only separator/garbage line :: (716) 872-4503</t>
+          <t>L19: isolated marker/symbol line :: 6"</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -755,7 +763,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -773,7 +781,11 @@
           <t>L4: isolated marker/symbol line :: M</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L30: symbol-only separator/garbage line :: (716) 872-4503</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -965,7 +977,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1013,7 +1025,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1051,12 +1063,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1441,7 +1453,7 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: M</t>
+          <t>L28: isolated marker/symbol line :: 6 ″</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -1472,7 +1484,7 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: F</t>
+          <t>L29: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1487,6 +1499,37 @@
       <c r="X23" s="1" t="inlineStr"/>
       <c r="Y23" s="1" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr"/>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+      <c r="G24" s="1" t="inlineStr"/>
+      <c r="H24" s="1" t="inlineStr"/>
+      <c r="I24" s="1" t="inlineStr"/>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
+      <c r="L24" s="1" t="inlineStr"/>
+      <c r="M24" s="1" t="inlineStr"/>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>L30: isolated marker/symbol line :: F</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr"/>
+      <c r="P24" s="1" t="inlineStr"/>
+      <c r="Q24" s="1" t="inlineStr"/>
+      <c r="R24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr"/>
+      <c r="T24" s="1" t="inlineStr"/>
+      <c r="U24" s="1" t="inlineStr"/>
+      <c r="V24" s="1" t="inlineStr"/>
+      <c r="W24" s="1" t="inlineStr"/>
+      <c r="X24" s="1" t="inlineStr"/>
+      <c r="Y24" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
